--- a/data/trans_orig/P36B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de café o té en 2016</t>
+          <t>Población según la frecuencia de consumo de café o té en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48646</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77861</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42006</t>
+          <t>41820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67299</t>
+          <t>70665</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96913</t>
+          <t>99881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137775</t>
+          <t>141317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>17389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29384</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>188303</t>
+          <t>187255</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220720</t>
+          <t>220243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195492</t>
+          <t>195312</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225648</t>
+          <t>227536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391629</t>
+          <t>393231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438966</t>
+          <t>438269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59855</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91883</t>
+          <t>93532</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59768</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91281</t>
+          <t>89965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126772</t>
+          <t>127658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170849</t>
+          <t>170415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>24742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>379492</t>
+          <t>379372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>416271</t>
+          <t>416529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>413705</t>
+          <t>415679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>448016</t>
+          <t>449257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>807617</t>
+          <t>808116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>857695</t>
+          <t>856877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49093</t>
+          <t>48842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75585</t>
+          <t>75073</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60290</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92886</t>
+          <t>90945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130749</t>
+          <t>128617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>24577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37608</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218675</t>
+          <t>218742</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249217</t>
+          <t>250007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247743</t>
+          <t>244689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277074</t>
+          <t>277534</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474840</t>
+          <t>477184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516296</t>
+          <t>518071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57815</t>
+          <t>58580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>77356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116883</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17884</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>281212</t>
+          <t>279916</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>313701</t>
+          <t>312666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>306941</t>
+          <t>305628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335940</t>
+          <t>336756</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>597002</t>
+          <t>597925</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>640146</t>
+          <t>643653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27768</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39664</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,42 +3739,42 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>7670</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7485</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>173473</t>
+          <t>173775</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>192239</t>
+          <t>193717</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>193228</t>
+          <t>193002</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>208840</t>
+          <t>207985</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>371781</t>
+          <t>372371</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>397309</t>
+          <t>397122</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>79348</t>
+          <t>79724</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110123</t>
+          <t>110083</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>116153</t>
+          <t>116390</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149886</t>
+          <t>148771</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>203136</t>
+          <t>204683</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>250980</t>
+          <t>251030</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118288</t>
+          <t>119201</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>151799</t>
+          <t>150952</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>111160</t>
+          <t>112303</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>145976</t>
+          <t>144173</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>242231</t>
+          <t>238722</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>286159</t>
+          <t>286749</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>46745</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>78116</t>
+          <t>80047</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>33670</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>60747</t>
+          <t>63182</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>88144</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>128793</t>
+          <t>129974</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10785</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24768</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>40349</t>
+          <t>40691</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>533704</t>
+          <t>534116</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>573331</t>
+          <t>573396</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>592739</t>
+          <t>593365</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>627216</t>
+          <t>626812</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1142066</t>
+          <t>1139246</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1191116</t>
+          <t>1190528</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>64009</t>
+          <t>65223</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>60276</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>76397</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>114221</t>
+          <t>115609</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32412</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>63072</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>665736</t>
+          <t>664862</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>702686</t>
+          <t>701339</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>713424</t>
+          <t>712788</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>749007</t>
+          <t>751149</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1391159</t>
+          <t>1389811</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1443445</t>
+          <t>1439994</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>436947</t>
+          <t>436231</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>516099</t>
+          <t>520007</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,47 +6201,47 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>455464</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>417344</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>499845</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
           <t>12,89%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>455464</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>413553</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>497229</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>878328</t>
+          <t>878727</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>988830</t>
+          <t>988479</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>94409</t>
+          <t>95601</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>134890</t>
+          <t>136455</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>69983</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>66102</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>92000</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>130312</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>182036</t>
+          <t>177579</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2648102</t>
+          <t>2649657</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2743943</t>
+          <t>2743991</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2854982</t>
+          <t>2855265</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2949996</t>
+          <t>2949108</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5538480</t>
+          <t>5528900</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5667884</t>
+          <t>5665908</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78087</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70665</t>
+          <t>68231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99881</t>
+          <t>98049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141317</t>
+          <t>138584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,47 +858,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3832</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3832</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9469</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>17731</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187255</t>
+          <t>188972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220243</t>
+          <t>220674</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195312</t>
+          <t>196504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227536</t>
+          <t>225820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393231</t>
+          <t>391614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>438269</t>
+          <t>436137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93532</t>
+          <t>91924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>92007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127658</t>
+          <t>127671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170415</t>
+          <t>172461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,47 +1653,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4313</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10648</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10377</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>379372</t>
+          <t>379509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>416529</t>
+          <t>416222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415679</t>
+          <t>415746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449257</t>
+          <t>447994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>808116</t>
+          <t>805364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>856877</t>
+          <t>855255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48842</t>
+          <t>49230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75073</t>
+          <t>76664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36910</t>
+          <t>36831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>93323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128617</t>
+          <t>131827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24577</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37527</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18589</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218742</t>
+          <t>218004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250007</t>
+          <t>248309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244689</t>
+          <t>246335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277534</t>
+          <t>277342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477184</t>
+          <t>474300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518071</t>
+          <t>517978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70038</t>
+          <t>68515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58580</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>80053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116137</t>
+          <t>118315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11246</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26112</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279916</t>
+          <t>282173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>312666</t>
+          <t>313403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>305628</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336756</t>
+          <t>336838</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>597925</t>
+          <t>598012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>643653</t>
+          <t>641096</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26207</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6591</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>173774</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>193717</t>
+          <t>193493</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>193002</t>
+          <t>193618</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>207985</t>
+          <t>208573</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>372371</t>
+          <t>372615</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>397122</t>
+          <t>397317</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>110083</t>
+          <t>108022</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>116390</t>
+          <t>116425</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>148771</t>
+          <t>149950</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>204683</t>
+          <t>203431</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>251030</t>
+          <t>249265</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>30882</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25452</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>119201</t>
+          <t>119742</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>150952</t>
+          <t>151913</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>112303</t>
+          <t>111799</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>144173</t>
+          <t>144627</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>238722</t>
+          <t>240836</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>286749</t>
+          <t>287062</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>47716</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>80047</t>
+          <t>78811</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>63182</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88144</t>
+          <t>88640</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>129018</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>28240</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>32599</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>40691</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>534116</t>
+          <t>536104</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>573396</t>
+          <t>573127</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>593365</t>
+          <t>593825</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>626812</t>
+          <t>626350</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1139246</t>
+          <t>1141555</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1190528</t>
+          <t>1191405</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>36191</t>
+          <t>36297</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>64997</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>60324</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>114192</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>14025</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>31950</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>36990</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>32737</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>61218</t>
+          <t>61584</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>664862</t>
+          <t>666120</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>701339</t>
+          <t>703089</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>712788</t>
+          <t>713983</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>751149</t>
+          <t>749984</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1389811</t>
+          <t>1390182</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1439994</t>
+          <t>1441205</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>436231</t>
+          <t>434989</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>520007</t>
+          <t>517337</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>417344</t>
+          <t>416658</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>499845</t>
+          <t>496841</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>878727</t>
+          <t>877144</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>988479</t>
+          <t>987209</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>95601</t>
+          <t>94413</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>136455</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>68907</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>103528</t>
+          <t>103727</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>103138</t>
+          <t>104304</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>177579</t>
+          <t>181261</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2649657</t>
+          <t>2652089</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2743991</t>
+          <t>2747420</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2855265</t>
+          <t>2851640</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2949108</t>
+          <t>2951726</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5528900</t>
+          <t>5538958</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5665908</t>
+          <t>5670506</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
